--- a/data/RIGI_planes_inversion.xlsx
+++ b/data/RIGI_planes_inversion.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve">anio</t>
   </si>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">https://www.argentina.gob.ar/economia/rigi</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14T14:55:36-03:00</t>
+    <t xml:space="preserve">2026-08-29T20:09:29-03:00</t>
   </si>
   <si>
     <t xml:space="preserve">petroleo</t>
@@ -206,6 +206,9 @@
     <t xml:space="preserve">Sin diferencias.</t>
   </si>
   <si>
+    <t xml:space="preserve">Minería: publicado=1473, calculado=1472, diferencia=1; Total desde subsectores: gráfico=3701, suma_subsectores=3700, diferencia=1</t>
+  </si>
+  <si>
     <t xml:space="preserve">campo</t>
   </si>
   <si>
@@ -254,13 +257,13 @@
     <t xml:space="preserve">last_modified</t>
   </si>
   <si>
-    <t xml:space="preserve">Fri, 14 Aug 2026 16:09:19 GMT</t>
+    <t xml:space="preserve">Sat, 29 Aug 2026 20:19:23 GMT</t>
   </si>
   <si>
     <t xml:space="preserve">html_bytes</t>
   </si>
   <si>
-    <t xml:space="preserve">84137</t>
+    <t xml:space="preserve">76172</t>
   </si>
   <si>
     <t xml:space="preserve">cantidad_intentos</t>
@@ -350,9 +353,6 @@
     <t xml:space="preserve">inconsistencias_detectadas</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninguna.</t>
-  </si>
-  <si>
     <t xml:space="preserve">cambios_referencia_2026</t>
   </si>
   <si>
@@ -362,16 +362,19 @@
     <t xml:space="preserve">advertencias_ejecucion</t>
   </si>
   <si>
+    <t xml:space="preserve">Ninguna.</t>
+  </si>
+  <si>
     <t xml:space="preserve">sha256_json_embebido</t>
   </si>
   <si>
-    <t xml:space="preserve">4d4cb72b3585bc2d72f993c99e8f3bf6165bb14dd24a50dad49c38bc8a13dafd</t>
+    <t xml:space="preserve">25cfef15cc20c42d34f5a7875a7eb674a699182e4fc9c32e6edef676e26e8b95</t>
   </si>
   <si>
     <t xml:space="preserve">sha256_html</t>
   </si>
   <si>
-    <t xml:space="preserve">d4e5a6e1039fae4c4e5a761563ca4e27d4683a62fbb81886ea4c78c1994caa85</t>
+    <t xml:space="preserve">22ade973790c5a71728f7f00feae76c55f901530af940249554cb88a7ae4c78c</t>
   </si>
   <si>
     <t xml:space="preserve">version_R</t>
@@ -399,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -424,8 +427,14 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF991B1B"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +449,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,13 +474,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -914,7 +929,7 @@
         <v>37</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
@@ -943,13 +958,13 @@
         <v>17</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
@@ -981,10 +996,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -1019,7 +1034,7 @@
         <v>527</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -1054,7 +1069,7 @@
         <v>527</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -1089,7 +1104,7 @@
         <v>527</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
@@ -1124,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
@@ -1159,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
@@ -1194,7 +1209,7 @@
         <v>252</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
@@ -1223,13 +1238,13 @@
         <v>17</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -1261,10 +1276,10 @@
         <v>228</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
@@ -1296,10 +1311,10 @@
         <v>419</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -1331,10 +1346,10 @@
         <v>948</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
@@ -1366,10 +1381,10 @@
         <v>105</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
@@ -1404,7 +1419,7 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
@@ -1439,7 +1454,7 @@
         <v>92</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
@@ -1474,7 +1489,7 @@
         <v>162</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
@@ -1503,13 +1518,13 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2277</v>
+        <v>2348</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
@@ -1541,10 +1556,10 @@
         <v>376</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -1579,7 +1594,7 @@
         <v>2579</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -1614,7 +1629,7 @@
         <v>2579</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -1649,7 +1664,7 @@
         <v>2579</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -1684,7 +1699,7 @@
         <v>130</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -1719,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1754,7 +1769,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1783,13 +1798,13 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>959</v>
+        <v>1090</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1821,10 +1836,10 @@
         <v>542</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1859,7 +1874,7 @@
         <v>3875</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1894,7 +1909,7 @@
         <v>3875</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1929,7 +1944,7 @@
         <v>3875</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1964,7 +1979,7 @@
         <v>66</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1999,7 +2014,7 @@
         <v>64</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -2034,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -2063,13 +2078,13 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>680</v>
+        <v>818</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2101,10 +2116,10 @@
         <v>491</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2139,7 +2154,7 @@
         <v>4128</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2174,7 +2189,7 @@
         <v>4128</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2209,7 +2224,7 @@
         <v>4128</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
@@ -2244,7 +2259,7 @@
         <v>8</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -2279,7 +2294,7 @@
         <v>24</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
@@ -10212,7 +10227,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>527</v>
@@ -10224,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>14</v>
@@ -10242,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3">
@@ -10253,10 +10268,10 @@
         <v>252</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>82</v>
@@ -10265,7 +10280,7 @@
         <v>92</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>228</v>
@@ -10283,7 +10298,7 @@
         <v>92</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="4">
@@ -10294,7 +10309,7 @@
         <v>162</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2579</v>
@@ -10306,7 +10321,7 @@
         <v>74</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2277</v>
+        <v>2348</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>376</v>
@@ -10324,7 +10339,7 @@
         <v>74</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
     </row>
     <row r="5">
@@ -10335,7 +10350,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>3875</v>
@@ -10347,7 +10362,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>959</v>
+        <v>1090</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>542</v>
@@ -10365,7 +10380,7 @@
         <v>64</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="6">
@@ -10376,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>4128</v>
@@ -10388,7 +10403,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>680</v>
+        <v>818</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>491</v>
@@ -10406,7 +10421,7 @@
         <v>24</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
     </row>
     <row r="7">
@@ -11676,10 +11691,10 @@
         <v>2024</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -11712,10 +11727,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -11724,7 +11739,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>0</v>
@@ -11741,7 +11756,7 @@
       <c r="W2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -11750,10 +11765,10 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
@@ -11762,16 +11777,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1472</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>92</v>
@@ -11786,10 +11801,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -11798,13 +11813,13 @@
         <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>3691</v>
+        <v>3700</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T3" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>0</v>
@@ -11812,11 +11827,11 @@
       <c r="V3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="W3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>62</v>
+      <c r="W3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -11824,10 +11839,10 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -11860,10 +11875,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>0</v>
@@ -11872,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
@@ -11889,7 +11904,7 @@
       <c r="W4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -11898,10 +11913,10 @@
         <v>2027</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -11934,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0</v>
@@ -11946,7 +11961,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>0</v>
@@ -11963,7 +11978,7 @@
       <c r="W5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -11972,10 +11987,10 @@
         <v>2028</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -12008,10 +12023,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0</v>
@@ -12020,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>0</v>
@@ -12037,7 +12052,7 @@
       <c r="W6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12111,7 +12126,7 @@
       <c r="W7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12185,7 +12200,7 @@
       <c r="W8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12259,7 +12274,7 @@
       <c r="W9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12333,7 +12348,7 @@
       <c r="W10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12407,7 +12422,7 @@
       <c r="W11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X11" s="4" t="s">
+      <c r="X11" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12481,7 +12496,7 @@
       <c r="W12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X12" s="4" t="s">
+      <c r="X12" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12555,7 +12570,7 @@
       <c r="W13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X13" s="4" t="s">
+      <c r="X13" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12629,7 +12644,7 @@
       <c r="W14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12703,7 +12718,7 @@
       <c r="W15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X15" s="4" t="s">
+      <c r="X15" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12777,7 +12792,7 @@
       <c r="W16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="X16" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12851,7 +12866,7 @@
       <c r="W17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X17" s="4" t="s">
+      <c r="X17" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12925,7 +12940,7 @@
       <c r="W18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -12999,7 +13014,7 @@
       <c r="W19" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X19" s="4" t="s">
+      <c r="X19" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13073,7 +13088,7 @@
       <c r="W20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X20" s="4" t="s">
+      <c r="X20" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13147,7 +13162,7 @@
       <c r="W21" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X21" s="4" t="s">
+      <c r="X21" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13221,7 +13236,7 @@
       <c r="W22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X22" s="4" t="s">
+      <c r="X22" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13295,7 +13310,7 @@
       <c r="W23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13369,7 +13384,7 @@
       <c r="W24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X24" s="4" t="s">
+      <c r="X24" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13443,7 +13458,7 @@
       <c r="W25" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X25" s="4" t="s">
+      <c r="X25" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13517,7 +13532,7 @@
       <c r="W26" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X26" s="4" t="s">
+      <c r="X26" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13591,7 +13606,7 @@
       <c r="W27" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X27" s="4" t="s">
+      <c r="X27" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13665,7 +13680,7 @@
       <c r="W28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X28" s="4" t="s">
+      <c r="X28" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13739,7 +13754,7 @@
       <c r="W29" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X29" s="4" t="s">
+      <c r="X29" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13813,7 +13828,7 @@
       <c r="W30" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X30" s="4" t="s">
+      <c r="X30" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13887,7 +13902,7 @@
       <c r="W31" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X31" s="4" t="s">
+      <c r="X31" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13961,7 +13976,7 @@
       <c r="W32" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X32" s="4" t="s">
+      <c r="X32" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -14035,7 +14050,7 @@
       <c r="W33" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X33" s="4" t="s">
+      <c r="X33" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -14109,7 +14124,7 @@
       <c r="W34" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X34" s="4" t="s">
+      <c r="X34" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -14133,225 +14148,225 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="4" t="s">
         <v>69</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>71</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="4" t="s">
         <v>73</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="4" t="s">
         <v>75</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="4" t="s">
         <v>77</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="4" t="s">
         <v>79</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="4" t="s">
         <v>81</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="4" t="s">
         <v>83</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>85</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>87</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="4" t="s">
         <v>89</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="4" t="s">
         <v>91</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="4" t="s">
         <v>93</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="4" t="s">
         <v>95</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="4" t="s">
         <v>97</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="4" t="s">
         <v>99</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="4" t="s">
         <v>101</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>102</v>
-      </c>
-      <c r="B22" s="4" t="s">
         <v>103</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="4" t="s">
         <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="4" t="s">
         <v>108</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>109</v>
+      <c r="B26" s="5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="4" t="s">
         <v>111</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>113</v>
       </c>
     </row>
@@ -14359,48 +14374,48 @@
       <c r="A29" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>111</v>
+      <c r="B29" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="4" t="s">
         <v>116</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="4" t="s">
         <v>118</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="4" t="s">
         <v>120</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="4" t="s">
         <v>122</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="4" t="s">
         <v>124</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_planes_inversion.xlsx
+++ b/data/RIGI_planes_inversion.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">anio</t>
   </si>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">https://www.argentina.gob.ar/economia/rigi</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29T20:09:29-03:00</t>
+    <t xml:space="preserve">2026-10-01T21:11:11-03:00</t>
   </si>
   <si>
     <t xml:space="preserve">petroleo</t>
@@ -104,6 +104,9 @@
     <t xml:space="preserve">Puerto</t>
   </si>
   <si>
+    <t xml:space="preserve">Fertilizantes</t>
+  </si>
+  <si>
     <t xml:space="preserve">energia_electrica</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t xml:space="preserve">upstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fertilizantes</t>
   </si>
   <si>
     <t xml:space="preserve">cobre</t>
@@ -257,13 +263,13 @@
     <t xml:space="preserve">last_modified</t>
   </si>
   <si>
-    <t xml:space="preserve">Sat, 29 Aug 2026 20:19:23 GMT</t>
+    <t xml:space="preserve">Thu, 01 Oct 2026 20:11:33 GMT</t>
   </si>
   <si>
     <t xml:space="preserve">html_bytes</t>
   </si>
   <si>
-    <t xml:space="preserve">76172</t>
+    <t xml:space="preserve">76485</t>
   </si>
   <si>
     <t xml:space="preserve">cantidad_intentos</t>
@@ -329,13 +335,13 @@
     <t xml:space="preserve">subsectores_detectados</t>
   </si>
   <si>
-    <t xml:space="preserve">Energía Eléctrica | Midstream | Upstream | Cobre | Litio | Oro y Plata | Siderurgia | Puerto</t>
+    <t xml:space="preserve">Energía Eléctrica | Midstream | Upstream | Cobre | Litio | Oro y Plata | Siderurgia | Puerto | Fertilizantes</t>
   </si>
   <si>
     <t xml:space="preserve">cantidad_filas_long</t>
   </si>
   <si>
-    <t xml:space="preserve">264</t>
+    <t xml:space="preserve">268</t>
   </si>
   <si>
     <t xml:space="preserve">cantidad_filas_wide</t>
@@ -368,13 +374,13 @@
     <t xml:space="preserve">sha256_json_embebido</t>
   </si>
   <si>
-    <t xml:space="preserve">25cfef15cc20c42d34f5a7875a7eb674a699182e4fc9c32e6edef676e26e8b95</t>
+    <t xml:space="preserve">ae00bd9f50ba17fa7b800545c04d9f060c41f0d0a2ac87c825c937e731fd0128</t>
   </si>
   <si>
     <t xml:space="preserve">sha256_html</t>
   </si>
   <si>
-    <t xml:space="preserve">22ade973790c5a71728f7f00feae76c55f901530af940249554cb88a7ae4c78c</t>
+    <t xml:space="preserve">02a3b80164b14523e8517ce961bf3174a968d178a375578efff691d00e905a21</t>
   </si>
   <si>
     <t xml:space="preserve">version_R</t>
@@ -494,8 +500,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K265" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K265"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K269" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K269"/>
   <tableColumns count="11">
     <tableColumn id="1" name="anio"/>
     <tableColumn id="2" name="sector_key"/>
@@ -514,9 +520,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:M34" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M34"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:N34" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:N34"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="anio"/>
     <tableColumn id="2" name="energia_electrica"/>
     <tableColumn id="3" name="petroleo_gas"/>
@@ -525,11 +531,12 @@
     <tableColumn id="6" name="infraestructura"/>
     <tableColumn id="7" name="midstream"/>
     <tableColumn id="8" name="upstream"/>
-    <tableColumn id="9" name="cobre"/>
-    <tableColumn id="10" name="litio"/>
-    <tableColumn id="11" name="oro_plata"/>
-    <tableColumn id="12" name="puerto"/>
-    <tableColumn id="13" name="total_anual"/>
+    <tableColumn id="9" name="fertilizantes"/>
+    <tableColumn id="10" name="cobre"/>
+    <tableColumn id="11" name="litio"/>
+    <tableColumn id="12" name="oro_plata"/>
+    <tableColumn id="13" name="puerto"/>
+    <tableColumn id="14" name="total_anual"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1489,7 +1496,7 @@
         <v>162</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
@@ -1521,10 +1528,10 @@
         <v>2348</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
@@ -1556,10 +1563,10 @@
         <v>376</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -1579,22 +1586,22 @@
         <v>2026</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>962</v>
+        <v>527</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2579</v>
+        <v>3251</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -1620,16 +1627,16 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1358</v>
+        <v>962</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2579</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -1655,16 +1662,16 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>259</v>
+        <v>1358</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>2579</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -1684,22 +1691,22 @@
         <v>2026</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>130</v>
+        <v>259</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>130</v>
+        <v>2579</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -1719,22 +1726,22 @@
         <v>2026</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1751,25 +1758,25 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5673</v>
+        <v>6196</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1789,22 +1796,22 @@
         <v>2027</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1090</v>
+        <v>36</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1632</v>
+        <v>36</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1830,16 +1837,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>542</v>
+        <v>1090</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1632</v>
+        <v>2210</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1859,22 +1866,22 @@
         <v>2027</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2362</v>
+        <v>542</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>3875</v>
+        <v>2210</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1894,22 +1901,22 @@
         <v>2027</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1141</v>
+        <v>578</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>3875</v>
+        <v>2210</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1935,16 +1942,16 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>372</v>
+        <v>2362</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>3875</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1964,22 +1971,22 @@
         <v>2027</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>66</v>
+        <v>1141</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>66</v>
+        <v>3875</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1999,22 +2006,22 @@
         <v>2027</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>64</v>
+        <v>372</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>64</v>
+        <v>3875</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -2031,25 +2038,25 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5469</v>
+        <v>6251</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -2066,25 +2073,25 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>818</v>
+        <v>64</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1309</v>
+        <v>64</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5469</v>
+        <v>6251</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2104,22 +2111,22 @@
         <v>2028</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1309</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2139,22 +2146,22 @@
         <v>2028</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2999</v>
+        <v>818</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>4128</v>
+        <v>2484</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2174,22 +2181,22 @@
         <v>2028</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>749</v>
+        <v>491</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4128</v>
+        <v>2484</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2209,22 +2216,22 @@
         <v>2028</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>380</v>
+        <v>1175</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4128</v>
+        <v>2484</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
@@ -2244,22 +2251,22 @@
         <v>2028</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>8</v>
+        <v>2999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>8</v>
+        <v>4128</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -2279,22 +2286,22 @@
         <v>2028</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>24</v>
+        <v>749</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>24</v>
+        <v>4128</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
@@ -2311,25 +2318,25 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>4128</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
@@ -2346,25 +2353,25 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>685</v>
+        <v>8</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>953</v>
+        <v>8</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -2381,25 +2388,25 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>268</v>
+        <v>24</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>953</v>
+        <v>24</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
@@ -2419,22 +2426,22 @@
         <v>2029</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2843</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>3278</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -2454,22 +2461,22 @@
         <v>2029</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>229</v>
+        <v>685</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>3278</v>
+        <v>1366</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -2489,22 +2496,22 @@
         <v>2029</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>3278</v>
+        <v>1366</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
@@ -2524,22 +2531,22 @@
         <v>2029</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0</v>
+        <v>1366</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -2559,22 +2566,22 @@
         <v>2029</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>21</v>
+        <v>2843</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>21</v>
+        <v>3278</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
@@ -2591,25 +2598,25 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0</v>
+        <v>3278</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -2626,25 +2633,25 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>685</v>
+        <v>206</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1033</v>
+        <v>3278</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
@@ -2661,25 +2668,25 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -2696,25 +2703,25 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>2223</v>
-      </c>
       <c r="F53" s="2" t="n">
-        <v>2450</v>
+        <v>21</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
@@ -2734,19 +2741,19 @@
         <v>2030</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>3485</v>
@@ -2769,19 +2776,19 @@
         <v>2030</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>37</v>
+        <v>685</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2450</v>
+        <v>1033</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>3485</v>
@@ -2804,19 +2811,19 @@
         <v>2030</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>3485</v>
@@ -2839,19 +2846,19 @@
         <v>2030</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2</v>
+        <v>2223</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>2</v>
+        <v>2450</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>3485</v>
@@ -2871,25 +2878,25 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
@@ -2906,25 +2913,25 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>685</v>
+        <v>37</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>915</v>
+        <v>2450</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -2941,25 +2948,25 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2976,25 +2983,25 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1144</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1503</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
@@ -3014,19 +3021,19 @@
         <v>2031</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>2418</v>
@@ -3049,19 +3056,19 @@
         <v>2031</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>20</v>
+        <v>685</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1503</v>
+        <v>915</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>2418</v>
@@ -3084,19 +3091,19 @@
         <v>2031</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>2418</v>
@@ -3119,19 +3126,19 @@
         <v>2031</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0</v>
+        <v>1144</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>2418</v>
@@ -3151,25 +3158,25 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -3186,25 +3193,25 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>685</v>
+        <v>20</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>958</v>
+        <v>1503</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
@@ -3221,25 +3228,25 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -3256,25 +3263,25 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -3294,19 +3301,19 @@
         <v>2032</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>1374</v>
@@ -3329,19 +3336,19 @@
         <v>2032</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>21</v>
+        <v>685</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>416</v>
+        <v>958</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>1374</v>
@@ -3364,19 +3371,19 @@
         <v>2032</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>1374</v>
@@ -3399,19 +3406,19 @@
         <v>2032</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>1374</v>
@@ -3431,25 +3438,25 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -3466,25 +3473,25 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>689</v>
+        <v>21</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>953</v>
+        <v>416</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3501,25 +3508,25 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
@@ -3536,25 +3543,25 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
@@ -3574,19 +3581,19 @@
         <v>2033</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>1058</v>
@@ -3609,19 +3616,19 @@
         <v>2033</v>
       </c>
       <c r="B79" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>14</v>
+        <v>689</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>105</v>
+        <v>953</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>1058</v>
@@ -3644,19 +3651,19 @@
         <v>2033</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>1058</v>
@@ -3679,19 +3686,19 @@
         <v>2033</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C81" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>1058</v>
@@ -3711,25 +3718,25 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3746,25 +3753,25 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>693</v>
+        <v>14</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>996</v>
+        <v>105</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -3781,25 +3788,25 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>996</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3816,25 +3823,25 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="H85" t="s">
         <v>13</v>
@@ -3854,19 +3861,19 @@
         <v>2034</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>1026</v>
@@ -3889,19 +3896,19 @@
         <v>2034</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18</v>
+        <v>693</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>30</v>
+        <v>996</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>1026</v>
@@ -3924,19 +3931,19 @@
         <v>2034</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>1026</v>
@@ -3959,19 +3966,19 @@
         <v>2034</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>1026</v>
@@ -3991,25 +3998,25 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -4026,25 +4033,25 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>698</v>
+        <v>18</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>949</v>
+        <v>30</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -4061,25 +4068,25 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -4096,25 +4103,25 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -4134,19 +4141,19 @@
         <v>2035</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>1001</v>
@@ -4169,19 +4176,19 @@
         <v>2035</v>
       </c>
       <c r="B95" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>22</v>
+        <v>698</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>52</v>
+        <v>949</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>1001</v>
@@ -4204,19 +4211,19 @@
         <v>2035</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>1001</v>
@@ -4239,19 +4246,19 @@
         <v>2035</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>1001</v>
@@ -4271,25 +4278,25 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C98" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
@@ -4306,25 +4313,25 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>702</v>
+        <v>22</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>858</v>
+        <v>52</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -4341,25 +4348,25 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -4376,25 +4383,25 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -4414,19 +4421,19 @@
         <v>2036</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>889</v>
@@ -4449,19 +4456,19 @@
         <v>2036</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17</v>
+        <v>702</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>31</v>
+        <v>858</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>889</v>
@@ -4484,19 +4491,19 @@
         <v>2036</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>889</v>
@@ -4519,19 +4526,19 @@
         <v>2036</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>889</v>
@@ -4551,25 +4558,25 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -4586,25 +4593,25 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D107" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>706</v>
-      </c>
       <c r="F107" s="2" t="n">
-        <v>862</v>
+        <v>31</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -4621,25 +4628,25 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>862</v>
+        <v>0</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -4656,25 +4663,25 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D109" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -4694,19 +4701,19 @@
         <v>2037</v>
       </c>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>894</v>
@@ -4729,19 +4736,19 @@
         <v>2037</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>21</v>
+        <v>706</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>32</v>
+        <v>862</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>894</v>
@@ -4764,19 +4771,19 @@
         <v>2037</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0</v>
+        <v>862</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>894</v>
@@ -4799,19 +4806,19 @@
         <v>2037</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>894</v>
@@ -4831,25 +4838,25 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C114" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H114" t="s">
         <v>13</v>
@@ -4866,25 +4873,25 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>711</v>
+        <v>21</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>867</v>
+        <v>32</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H115" t="s">
         <v>13</v>
@@ -4901,25 +4908,25 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C116" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H116" t="s">
         <v>13</v>
@@ -4936,25 +4943,25 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B117" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H117" t="s">
         <v>13</v>
@@ -4974,19 +4981,19 @@
         <v>2038</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>896</v>
@@ -5009,19 +5016,19 @@
         <v>2038</v>
       </c>
       <c r="B119" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18</v>
+        <v>711</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>29</v>
+        <v>867</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>896</v>
@@ -5044,19 +5051,19 @@
         <v>2038</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>896</v>
@@ -5079,19 +5086,19 @@
         <v>2038</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>896</v>
@@ -5111,25 +5118,25 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
@@ -5146,25 +5153,25 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C123" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>716</v>
+        <v>18</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>872</v>
+        <v>29</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="H123" t="s">
         <v>13</v>
@@ -5181,25 +5188,25 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="H124" t="s">
         <v>13</v>
@@ -5216,25 +5223,25 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B125" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D125" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="H125" t="s">
         <v>13</v>
@@ -5254,19 +5261,19 @@
         <v>2039</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>903</v>
@@ -5289,19 +5296,19 @@
         <v>2039</v>
       </c>
       <c r="B127" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>18</v>
+        <v>716</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>31</v>
+        <v>872</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>903</v>
@@ -5324,19 +5331,19 @@
         <v>2039</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>903</v>
@@ -5359,19 +5366,19 @@
         <v>2039</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C129" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>903</v>
@@ -5391,25 +5398,25 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H130" t="s">
         <v>13</v>
@@ -5426,25 +5433,25 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C131" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>720</v>
+        <v>18</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>876</v>
+        <v>31</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H131" t="s">
         <v>13</v>
@@ -5461,25 +5468,25 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H132" t="s">
         <v>13</v>
@@ -5496,25 +5503,25 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B133" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D133" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H133" t="s">
         <v>13</v>
@@ -5534,19 +5541,19 @@
         <v>2040</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D134" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>901</v>
@@ -5569,19 +5576,19 @@
         <v>2040</v>
       </c>
       <c r="B135" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>14</v>
+        <v>720</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>25</v>
+        <v>876</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>901</v>
@@ -5604,19 +5611,19 @@
         <v>2040</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D136" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>901</v>
@@ -5639,19 +5646,19 @@
         <v>2040</v>
       </c>
       <c r="B137" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D137" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>901</v>
@@ -5671,25 +5678,25 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C138" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="H138" t="s">
         <v>13</v>
@@ -5706,25 +5713,25 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>725</v>
+        <v>14</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>881</v>
+        <v>25</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="H139" t="s">
         <v>13</v>
@@ -5741,25 +5748,25 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>881</v>
+        <v>0</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="H140" t="s">
         <v>13</v>
@@ -5776,25 +5783,25 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B141" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D141" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="H141" t="s">
         <v>13</v>
@@ -5814,19 +5821,19 @@
         <v>2041</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D142" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>908</v>
@@ -5849,19 +5856,19 @@
         <v>2041</v>
       </c>
       <c r="B143" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C143" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>16</v>
+        <v>725</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>27</v>
+        <v>881</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>908</v>
@@ -5884,19 +5891,19 @@
         <v>2041</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0</v>
+        <v>881</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>908</v>
@@ -5919,19 +5926,19 @@
         <v>2041</v>
       </c>
       <c r="B145" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C145" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" t="s">
+        <v>21</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F145" s="2" t="n">
         <v>27</v>
-      </c>
-      <c r="D145" t="s">
-        <v>28</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>908</v>
@@ -5951,25 +5958,25 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C146" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D146" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="H146" t="s">
         <v>13</v>
@@ -5986,25 +5993,25 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C147" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D147" t="s">
-        <v>17</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>730</v>
-      </c>
       <c r="F147" s="2" t="n">
-        <v>730</v>
+        <v>27</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="H147" t="s">
         <v>13</v>
@@ -6021,25 +6028,25 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
@@ -6056,25 +6063,25 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B149" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D149" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="H149" t="s">
         <v>13</v>
@@ -6094,19 +6101,19 @@
         <v>2042</v>
       </c>
       <c r="B150" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G150" s="2" t="n">
         <v>760</v>
@@ -6129,19 +6136,19 @@
         <v>2042</v>
       </c>
       <c r="B151" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>19</v>
+        <v>730</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>30</v>
+        <v>730</v>
       </c>
       <c r="G151" s="2" t="n">
         <v>760</v>
@@ -6164,19 +6171,19 @@
         <v>2042</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C152" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="G152" s="2" t="n">
         <v>760</v>
@@ -6199,19 +6206,19 @@
         <v>2042</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G153" s="2" t="n">
         <v>760</v>
@@ -6231,25 +6238,25 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B154" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C154" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="H154" t="s">
         <v>13</v>
@@ -6266,25 +6273,25 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C155" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>735</v>
+        <v>19</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>735</v>
+        <v>30</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="H155" t="s">
         <v>13</v>
@@ -6301,25 +6308,25 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="H156" t="s">
         <v>13</v>
@@ -6336,25 +6343,25 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B157" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D157" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="H157" t="s">
         <v>13</v>
@@ -6374,19 +6381,19 @@
         <v>2043</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D158" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G158" s="2" t="n">
         <v>808</v>
@@ -6409,19 +6416,19 @@
         <v>2043</v>
       </c>
       <c r="B159" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D159" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>62</v>
+        <v>735</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>73</v>
+        <v>735</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>808</v>
@@ -6444,19 +6451,19 @@
         <v>2043</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D160" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>808</v>
@@ -6479,19 +6486,19 @@
         <v>2043</v>
       </c>
       <c r="B161" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C161" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>808</v>
@@ -6511,25 +6518,25 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C162" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="H162" t="s">
         <v>13</v>
@@ -6546,25 +6553,25 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C163" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>740</v>
+        <v>62</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>740</v>
+        <v>73</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="H163" t="s">
         <v>13</v>
@@ -6581,25 +6588,25 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C164" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="H164" t="s">
         <v>13</v>
@@ -6616,25 +6623,25 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B165" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C165" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D165" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="H165" t="s">
         <v>13</v>
@@ -6654,19 +6661,19 @@
         <v>2044</v>
       </c>
       <c r="B166" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D166" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>834</v>
@@ -6689,19 +6696,19 @@
         <v>2044</v>
       </c>
       <c r="B167" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D167" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>27</v>
+        <v>740</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>94</v>
+        <v>740</v>
       </c>
       <c r="G167" s="2" t="n">
         <v>834</v>
@@ -6724,19 +6731,19 @@
         <v>2044</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D168" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="G168" s="2" t="n">
         <v>834</v>
@@ -6759,19 +6766,19 @@
         <v>2044</v>
       </c>
       <c r="B169" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C169" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G169" s="2" t="n">
         <v>834</v>
@@ -6791,25 +6798,25 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B170" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C170" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D170" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="H170" t="s">
         <v>13</v>
@@ -6826,25 +6833,25 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C171" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>745</v>
+        <v>27</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>745</v>
+        <v>94</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="H171" t="s">
         <v>13</v>
@@ -6861,25 +6868,25 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C172" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="H172" t="s">
         <v>13</v>
@@ -6896,25 +6903,25 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B173" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D173" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="H173" t="s">
         <v>13</v>
@@ -6934,19 +6941,19 @@
         <v>2045</v>
       </c>
       <c r="B174" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G174" s="2" t="n">
         <v>773</v>
@@ -6969,19 +6976,19 @@
         <v>2045</v>
       </c>
       <c r="B175" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C175" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>27</v>
+        <v>745</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>28</v>
+        <v>745</v>
       </c>
       <c r="G175" s="2" t="n">
         <v>773</v>
@@ -7004,19 +7011,19 @@
         <v>2045</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D176" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="G176" s="2" t="n">
         <v>773</v>
@@ -7039,19 +7046,19 @@
         <v>2045</v>
       </c>
       <c r="B177" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C177" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D177" t="s">
+        <v>21</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="2" t="n">
         <v>28</v>
-      </c>
-      <c r="E177" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="G177" s="2" t="n">
         <v>773</v>
@@ -7071,25 +7078,25 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B178" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C178" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H178" t="s">
         <v>13</v>
@@ -7106,25 +7113,25 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C179" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>751</v>
+        <v>27</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>751</v>
+        <v>28</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H179" t="s">
         <v>13</v>
@@ -7141,25 +7148,25 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C180" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H180" t="s">
         <v>13</v>
@@ -7176,25 +7183,25 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B181" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C181" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D181" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="H181" t="s">
         <v>13</v>
@@ -7214,19 +7221,19 @@
         <v>2046</v>
       </c>
       <c r="B182" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D182" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G182" s="2" t="n">
         <v>779</v>
@@ -7249,19 +7256,19 @@
         <v>2046</v>
       </c>
       <c r="B183" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C183" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D183" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>27</v>
+        <v>751</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>28</v>
+        <v>751</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>779</v>
@@ -7284,19 +7291,19 @@
         <v>2046</v>
       </c>
       <c r="B184" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C184" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D184" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G184" s="2" t="n">
         <v>779</v>
@@ -7319,19 +7326,19 @@
         <v>2046</v>
       </c>
       <c r="B185" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C185" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D185" t="s">
+        <v>21</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="2" t="n">
         <v>28</v>
-      </c>
-      <c r="E185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="G185" s="2" t="n">
         <v>779</v>
@@ -7351,25 +7358,25 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C186" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="H186" t="s">
         <v>13</v>
@@ -7386,25 +7393,25 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C187" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>757</v>
+        <v>27</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>757</v>
+        <v>28</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="H187" t="s">
         <v>13</v>
@@ -7421,25 +7428,25 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C188" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="H188" t="s">
         <v>13</v>
@@ -7456,25 +7463,25 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B189" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D189" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="H189" t="s">
         <v>13</v>
@@ -7494,19 +7501,19 @@
         <v>2047</v>
       </c>
       <c r="B190" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D190" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G190" s="2" t="n">
         <v>765</v>
@@ -7529,19 +7536,19 @@
         <v>2047</v>
       </c>
       <c r="B191" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C191" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D191" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>7</v>
+        <v>757</v>
       </c>
       <c r="F191" s="2" t="n">
-        <v>8</v>
+        <v>757</v>
       </c>
       <c r="G191" s="2" t="n">
         <v>765</v>
@@ -7564,19 +7571,19 @@
         <v>2047</v>
       </c>
       <c r="B192" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C192" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D192" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="G192" s="2" t="n">
         <v>765</v>
@@ -7599,19 +7606,19 @@
         <v>2047</v>
       </c>
       <c r="B193" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C193" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D193" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G193" s="2" t="n">
         <v>765</v>
@@ -7631,25 +7638,25 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B194" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C194" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D194" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="H194" t="s">
         <v>13</v>
@@ -7666,25 +7673,25 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C195" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D195" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>436</v>
+        <v>7</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>436</v>
+        <v>8</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="H195" t="s">
         <v>13</v>
@@ -7701,25 +7708,25 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C196" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="H196" t="s">
         <v>13</v>
@@ -7736,25 +7743,25 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B197" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C197" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D197" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="H197" t="s">
         <v>13</v>
@@ -7774,19 +7781,19 @@
         <v>2048</v>
       </c>
       <c r="B198" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D198" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G198" s="2" t="n">
         <v>444</v>
@@ -7809,19 +7816,19 @@
         <v>2048</v>
       </c>
       <c r="B199" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C199" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D199" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>7</v>
+        <v>436</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>8</v>
+        <v>436</v>
       </c>
       <c r="G199" s="2" t="n">
         <v>444</v>
@@ -7844,19 +7851,19 @@
         <v>2048</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D200" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="G200" s="2" t="n">
         <v>444</v>
@@ -7879,19 +7886,19 @@
         <v>2048</v>
       </c>
       <c r="B201" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C201" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D201" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G201" s="2" t="n">
         <v>444</v>
@@ -7911,25 +7918,25 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B202" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C202" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D202" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="H202" t="s">
         <v>13</v>
@@ -7946,25 +7953,25 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C203" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D203" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="H203" t="s">
         <v>13</v>
@@ -7981,16 +7988,16 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>0</v>
@@ -7999,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="H204" t="s">
         <v>13</v>
@@ -8016,25 +8023,25 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B205" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C205" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D205" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="H205" t="s">
         <v>13</v>
@@ -8054,19 +8061,19 @@
         <v>2049</v>
       </c>
       <c r="B206" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C206" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D206" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G206" s="2" t="n">
         <v>8</v>
@@ -8089,19 +8096,19 @@
         <v>2049</v>
       </c>
       <c r="B207" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C207" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D207" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G207" s="2" t="n">
         <v>8</v>
@@ -8124,13 +8131,13 @@
         <v>2049</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D208" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>0</v>
@@ -8159,19 +8166,19 @@
         <v>2049</v>
       </c>
       <c r="B209" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C209" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D209" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G209" s="2" t="n">
         <v>8</v>
@@ -8191,22 +8198,22 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B210" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C210" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D210" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G210" s="2" t="n">
         <v>8</v>
@@ -8226,22 +8233,22 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C211" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D211" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G211" s="2" t="n">
         <v>8</v>
@@ -8261,16 +8268,16 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>0</v>
@@ -8296,22 +8303,22 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B213" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C213" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D213" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G213" s="2" t="n">
         <v>8</v>
@@ -8334,19 +8341,19 @@
         <v>2050</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C214" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D214" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G214" s="2" t="n">
         <v>8</v>
@@ -8369,19 +8376,19 @@
         <v>2050</v>
       </c>
       <c r="B215" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C215" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D215" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G215" s="2" t="n">
         <v>8</v>
@@ -8404,13 +8411,13 @@
         <v>2050</v>
       </c>
       <c r="B216" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C216" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D216" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0</v>
@@ -8439,19 +8446,19 @@
         <v>2050</v>
       </c>
       <c r="B217" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C217" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D217" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>8</v>
@@ -8471,22 +8478,22 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B218" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C218" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D218" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G218" s="2" t="n">
         <v>8</v>
@@ -8506,22 +8513,22 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C219" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G219" s="2" t="n">
         <v>8</v>
@@ -8541,16 +8548,16 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C220" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>0</v>
@@ -8576,22 +8583,22 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B221" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D221" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G221" s="2" t="n">
         <v>8</v>
@@ -8614,19 +8621,19 @@
         <v>2051</v>
       </c>
       <c r="B222" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C222" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D222" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G222" s="2" t="n">
         <v>8</v>
@@ -8649,19 +8656,19 @@
         <v>2051</v>
       </c>
       <c r="B223" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C223" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D223" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G223" s="2" t="n">
         <v>8</v>
@@ -8684,13 +8691,13 @@
         <v>2051</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C224" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D224" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>0</v>
@@ -8719,19 +8726,19 @@
         <v>2051</v>
       </c>
       <c r="B225" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C225" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D225" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G225" s="2" t="n">
         <v>8</v>
@@ -8751,22 +8758,22 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B226" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C226" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D226" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G226" s="2" t="n">
         <v>8</v>
@@ -8786,22 +8793,22 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B227" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C227" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D227" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G227" s="2" t="n">
         <v>8</v>
@@ -8821,16 +8828,16 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B228" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C228" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>0</v>
@@ -8856,22 +8863,22 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B229" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C229" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D229" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G229" s="2" t="n">
         <v>8</v>
@@ -8894,19 +8901,19 @@
         <v>2052</v>
       </c>
       <c r="B230" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D230" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G230" s="2" t="n">
         <v>8</v>
@@ -8929,19 +8936,19 @@
         <v>2052</v>
       </c>
       <c r="B231" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C231" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D231" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>8</v>
@@ -8964,13 +8971,13 @@
         <v>2052</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C232" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D232" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>0</v>
@@ -8999,19 +9006,19 @@
         <v>2052</v>
       </c>
       <c r="B233" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C233" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D233" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>8</v>
@@ -9031,22 +9038,22 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B234" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C234" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D234" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E234" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G234" s="2" t="n">
         <v>8</v>
@@ -9066,22 +9073,22 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C235" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D235" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G235" s="2" t="n">
         <v>8</v>
@@ -9101,16 +9108,16 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B236" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C236" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E236" s="2" t="n">
         <v>0</v>
@@ -9136,22 +9143,22 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B237" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C237" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D237" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>8</v>
@@ -9174,19 +9181,19 @@
         <v>2053</v>
       </c>
       <c r="B238" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C238" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D238" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G238" s="2" t="n">
         <v>8</v>
@@ -9209,19 +9216,19 @@
         <v>2053</v>
       </c>
       <c r="B239" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D239" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F239" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G239" s="2" t="n">
         <v>8</v>
@@ -9244,13 +9251,13 @@
         <v>2053</v>
       </c>
       <c r="B240" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C240" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D240" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E240" s="2" t="n">
         <v>0</v>
@@ -9279,19 +9286,19 @@
         <v>2053</v>
       </c>
       <c r="B241" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C241" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D241" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G241" s="2" t="n">
         <v>8</v>
@@ -9311,22 +9318,22 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B242" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C242" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D242" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G242" s="2" t="n">
         <v>8</v>
@@ -9346,22 +9353,22 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C243" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D243" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F243" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G243" s="2" t="n">
         <v>8</v>
@@ -9381,16 +9388,16 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C244" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>0</v>
@@ -9416,22 +9423,22 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B245" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C245" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D245" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F245" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G245" s="2" t="n">
         <v>8</v>
@@ -9454,19 +9461,19 @@
         <v>2054</v>
       </c>
       <c r="B246" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C246" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D246" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F246" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G246" s="2" t="n">
         <v>8</v>
@@ -9489,19 +9496,19 @@
         <v>2054</v>
       </c>
       <c r="B247" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C247" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D247" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>8</v>
@@ -9524,13 +9531,13 @@
         <v>2054</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C248" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D248" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E248" s="2" t="n">
         <v>0</v>
@@ -9559,19 +9566,19 @@
         <v>2054</v>
       </c>
       <c r="B249" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C249" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D249" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G249" s="2" t="n">
         <v>8</v>
@@ -9591,25 +9598,25 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B250" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C250" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D250" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G250" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H250" t="s">
         <v>13</v>
@@ -9626,25 +9633,25 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B251" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C251" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D251" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G251" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H251" t="s">
         <v>13</v>
@@ -9661,16 +9668,16 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C252" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>0</v>
@@ -9679,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="G252" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H252" t="s">
         <v>13</v>
@@ -9696,25 +9703,25 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B253" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C253" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D253" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F253" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G253" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H253" t="s">
         <v>13</v>
@@ -9734,19 +9741,19 @@
         <v>2055</v>
       </c>
       <c r="B254" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C254" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D254" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E254" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F254" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G254" s="2" t="n">
         <v>7</v>
@@ -9769,19 +9776,19 @@
         <v>2055</v>
       </c>
       <c r="B255" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C255" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D255" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F255" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G255" s="2" t="n">
         <v>7</v>
@@ -9804,13 +9811,13 @@
         <v>2055</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C256" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D256" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E256" s="2" t="n">
         <v>0</v>
@@ -9839,19 +9846,19 @@
         <v>2055</v>
       </c>
       <c r="B257" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D257" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E257" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G257" s="2" t="n">
         <v>7</v>
@@ -9871,25 +9878,25 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B258" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C258" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D258" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G258" s="2" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H258" t="s">
         <v>13</v>
@@ -9906,25 +9913,25 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C259" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D259" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H259" t="s">
         <v>13</v>
@@ -9941,16 +9948,16 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B260" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C260" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E260" s="2" t="n">
         <v>0</v>
@@ -9959,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H260" t="s">
         <v>13</v>
@@ -9976,25 +9983,25 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B261" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C261" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D261" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E261" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F261" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G261" s="2" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H261" t="s">
         <v>13</v>
@@ -10014,19 +10021,19 @@
         <v>2056</v>
       </c>
       <c r="B262" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C262" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D262" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E262" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F262" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G262" s="2" t="n">
         <v>44</v>
@@ -10049,19 +10056,19 @@
         <v>2056</v>
       </c>
       <c r="B263" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C263" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D263" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F263" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G263" s="2" t="n">
         <v>44</v>
@@ -10084,13 +10091,13 @@
         <v>2056</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C264" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D264" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E264" s="2" t="n">
         <v>0</v>
@@ -10119,19 +10126,19 @@
         <v>2056</v>
       </c>
       <c r="B265" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C265" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D265" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E265" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F265" s="2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G265" s="2" t="n">
         <v>44</v>
@@ -10146,6 +10153,146 @@
         <v>1</v>
       </c>
       <c r="K265" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B266" t="s">
+        <v>19</v>
+      </c>
+      <c r="C266" t="s">
+        <v>20</v>
+      </c>
+      <c r="D266" t="s">
+        <v>22</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H266" t="s">
+        <v>13</v>
+      </c>
+      <c r="I266" t="s">
+        <v>14</v>
+      </c>
+      <c r="J266" t="b">
+        <v>1</v>
+      </c>
+      <c r="K266" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B267" t="s">
+        <v>19</v>
+      </c>
+      <c r="C267" t="s">
+        <v>20</v>
+      </c>
+      <c r="D267" t="s">
+        <v>23</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H267" t="s">
+        <v>13</v>
+      </c>
+      <c r="I267" t="s">
+        <v>14</v>
+      </c>
+      <c r="J267" t="b">
+        <v>1</v>
+      </c>
+      <c r="K267" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B268" t="s">
+        <v>24</v>
+      </c>
+      <c r="C268" t="s">
+        <v>25</v>
+      </c>
+      <c r="D268" t="s">
+        <v>25</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H268" t="s">
+        <v>13</v>
+      </c>
+      <c r="I268" t="s">
+        <v>14</v>
+      </c>
+      <c r="J268" t="b">
+        <v>1</v>
+      </c>
+      <c r="K268" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B269" t="s">
+        <v>26</v>
+      </c>
+      <c r="C269" t="s">
+        <v>27</v>
+      </c>
+      <c r="D269" t="s">
+        <v>28</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H269" t="s">
+        <v>13</v>
+      </c>
+      <c r="I269" t="s">
+        <v>14</v>
+      </c>
+      <c r="J269" t="b">
+        <v>1</v>
+      </c>
+      <c r="K269" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10176,6 +10323,7 @@
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -10183,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
@@ -10195,28 +10343,31 @@
         <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -10244,19 +10395,20 @@
       <c r="H2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>374</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>612</v>
       </c>
     </row>
@@ -10285,19 +10437,20 @@
       <c r="H3" s="2" t="n">
         <v>228</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="n">
         <v>419</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>948</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>3701</v>
       </c>
     </row>
@@ -10309,7 +10462,7 @@
         <v>162</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2579</v>
@@ -10327,19 +10480,22 @@
         <v>376</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>962</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>1358</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>259</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>5669</v>
+      <c r="N4" s="2" t="n">
+        <v>6196</v>
       </c>
     </row>
     <row r="5">
@@ -10350,7 +10506,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1632</v>
+        <v>2210</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>3875</v>
@@ -10368,19 +10524,22 @@
         <v>542</v>
       </c>
       <c r="I5" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>2362</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>1141</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>372</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>5673</v>
+      <c r="N5" s="2" t="n">
+        <v>6251</v>
       </c>
     </row>
     <row r="6">
@@ -10391,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1309</v>
+        <v>2484</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>4128</v>
@@ -10409,19 +10568,22 @@
         <v>491</v>
       </c>
       <c r="I6" s="2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>2999</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>749</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>5469</v>
+      <c r="N6" s="2" t="n">
+        <v>6644</v>
       </c>
     </row>
     <row r="7">
@@ -10432,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>953</v>
+        <v>1366</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>3278</v>
@@ -10450,19 +10612,22 @@
         <v>268</v>
       </c>
       <c r="I7" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>2843</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>229</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>4252</v>
+      <c r="N7" s="2" t="n">
+        <v>4665</v>
       </c>
     </row>
     <row r="8">
@@ -10490,19 +10655,20 @@
       <c r="H8" s="2" t="n">
         <v>348</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="n">
         <v>2223</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>3485</v>
       </c>
     </row>
@@ -10531,19 +10697,20 @@
       <c r="H9" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="n">
         <v>1144</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>339</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
         <v>2418</v>
       </c>
     </row>
@@ -10572,19 +10739,20 @@
       <c r="H10" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>384</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>1374</v>
       </c>
     </row>
@@ -10613,19 +10781,20 @@
       <c r="H11" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
         <v>1058</v>
       </c>
     </row>
@@ -10654,19 +10823,20 @@
       <c r="H12" s="2" t="n">
         <v>303</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
         <v>1026</v>
       </c>
     </row>
@@ -10695,19 +10865,20 @@
       <c r="H13" s="2" t="n">
         <v>251</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -10736,19 +10907,20 @@
       <c r="H14" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="I14" s="2"/>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
         <v>889</v>
       </c>
     </row>
@@ -10777,19 +10949,20 @@
       <c r="H15" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
         <v>894</v>
       </c>
     </row>
@@ -10818,19 +10991,20 @@
       <c r="H16" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
         <v>896</v>
       </c>
     </row>
@@ -10859,19 +11033,20 @@
       <c r="H17" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
         <v>903</v>
       </c>
     </row>
@@ -10900,19 +11075,20 @@
       <c r="H18" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
         <v>901</v>
       </c>
     </row>
@@ -10941,19 +11117,20 @@
       <c r="H19" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
         <v>908</v>
       </c>
     </row>
@@ -10982,19 +11159,20 @@
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
         <v>760</v>
       </c>
     </row>
@@ -11023,19 +11201,20 @@
       <c r="H21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
         <v>808</v>
       </c>
     </row>
@@ -11064,19 +11243,20 @@
       <c r="H22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="J22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
         <v>834</v>
       </c>
     </row>
@@ -11105,19 +11285,20 @@
       <c r="H23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I23" s="2"/>
       <c r="J23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
         <v>773</v>
       </c>
     </row>
@@ -11146,19 +11327,20 @@
       <c r="H24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
         <v>779</v>
       </c>
     </row>
@@ -11187,19 +11369,20 @@
       <c r="H25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
         <v>765</v>
       </c>
     </row>
@@ -11228,19 +11411,20 @@
       <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
         <v>444</v>
       </c>
     </row>
@@ -11269,19 +11453,20 @@
       <c r="H27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I27" s="2"/>
       <c r="J27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11310,19 +11495,20 @@
       <c r="H28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I28" s="2"/>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11351,19 +11537,20 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I29" s="2"/>
       <c r="J29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11392,19 +11579,20 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I30" s="2"/>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11433,19 +11621,20 @@
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I31" s="2"/>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11474,19 +11663,20 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11515,19 +11705,20 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" s="2"/>
       <c r="J33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11556,19 +11747,20 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" s="2"/>
       <c r="J34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="n">
         <v>44</v>
       </c>
     </row>
@@ -11617,73 +11809,73 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
@@ -11757,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -11831,7 +12023,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -11839,10 +12031,10 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -11875,10 +12067,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>0</v>
@@ -11887,7 +12079,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
@@ -11905,7 +12097,7 @@
         <v>1</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -11913,10 +12105,10 @@
         <v>2027</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1632</v>
+        <v>2210</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1632</v>
+        <v>2210</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -11949,10 +12141,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0</v>
@@ -11961,7 +12153,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>0</v>
@@ -11979,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -11987,10 +12179,10 @@
         <v>2028</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1309</v>
+        <v>2484</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1309</v>
+        <v>2484</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -12023,10 +12215,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0</v>
@@ -12035,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>0</v>
@@ -12053,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -12061,10 +12253,10 @@
         <v>2029</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>953</v>
+        <v>1366</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>953</v>
+        <v>1366</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
@@ -12097,10 +12289,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0</v>
@@ -12109,7 +12301,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>0</v>
@@ -12127,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -12201,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -12275,7 +12467,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -12349,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -12423,7 +12615,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -12497,7 +12689,7 @@
         <v>1</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -12571,7 +12763,7 @@
         <v>1</v>
       </c>
       <c r="X13" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -12645,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -12719,7 +12911,7 @@
         <v>1</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -12793,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -12867,7 +13059,7 @@
         <v>1</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -12941,7 +13133,7 @@
         <v>1</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -13015,7 +13207,7 @@
         <v>1</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -13089,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="X20" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -13163,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="X21" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
@@ -13237,7 +13429,7 @@
         <v>1</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
@@ -13311,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24">
@@ -13385,7 +13577,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -13459,7 +13651,7 @@
         <v>1</v>
       </c>
       <c r="X25" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -13533,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="X26" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -13607,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
@@ -13681,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="X28" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -13755,7 +13947,7 @@
         <v>1</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
@@ -13829,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
@@ -13903,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -13977,7 +14169,7 @@
         <v>1</v>
       </c>
       <c r="X32" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -14051,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="X33" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
@@ -14125,7 +14317,7 @@
         <v>1</v>
       </c>
       <c r="X34" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -14148,15 +14340,15 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>13</v>
@@ -14164,7 +14356,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>13</v>
@@ -14172,7 +14364,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>14</v>
@@ -14180,242 +14372,242 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
